--- a/resources/templates/standard/F2100-14.xlsx
+++ b/resources/templates/standard/F2100-14.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>자격인증 평가 (갑지)</t>
   </si>
@@ -898,10 +901,12 @@
     </row>
     <row r="2" ht="39.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -955,18 +960,18 @@
     <row r="4" ht="21.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="2"/>
@@ -974,16 +979,16 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4" s="10"/>
       <c r="V4" s="10"/>
@@ -994,18 +999,18 @@
     <row r="5" ht="21.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="2"/>
@@ -1014,7 +1019,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="7"/>
       <c r="P5" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="9"/>
@@ -1056,7 +1061,7 @@
     <row r="7" ht="20.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -1085,7 +1090,7 @@
     <row r="8" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -1095,7 +1100,7 @@
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
       <c r="J8" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" s="14"/>
       <c r="L8" s="14"/>
@@ -1109,7 +1114,7 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="1"/>
@@ -1126,19 +1131,19 @@
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K9" s="14"/>
       <c r="L9" s="14"/>
       <c r="M9" s="14"/>
       <c r="N9" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="14"/>
       <c r="Q9" s="14"/>
       <c r="R9" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S9" s="14"/>
       <c r="T9" s="14"/>
@@ -1151,7 +1156,7 @@
     <row r="10" ht="45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
@@ -1161,19 +1166,19 @@
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
       <c r="J10" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
       <c r="R10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
@@ -1213,7 +1218,7 @@
     <row r="12" ht="20.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -1242,7 +1247,7 @@
     <row r="13" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -1252,7 +1257,7 @@
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
       <c r="J13" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
@@ -1266,7 +1271,7 @@
       <c r="T13" s="14"/>
       <c r="U13" s="14"/>
       <c r="V13" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W13" s="5"/>
       <c r="X13" s="1"/>
@@ -1283,19 +1288,19 @@
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
       <c r="N14" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O14" s="14"/>
       <c r="P14" s="14"/>
       <c r="Q14" s="14"/>
       <c r="R14" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S14" s="14"/>
       <c r="T14" s="14"/>
@@ -1308,7 +1313,7 @@
     <row r="15" ht="45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -1318,19 +1323,19 @@
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
       <c r="J15" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
       <c r="N15" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
       <c r="R15" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S15" s="15"/>
       <c r="T15" s="15"/>
@@ -1370,7 +1375,7 @@
     <row r="17" ht="20.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -1399,7 +1404,7 @@
     <row r="18" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -1409,7 +1414,7 @@
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="J18" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
@@ -1423,7 +1428,7 @@
       <c r="T18" s="14"/>
       <c r="U18" s="14"/>
       <c r="V18" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W18" s="5"/>
       <c r="X18" s="1"/>
@@ -1440,22 +1445,22 @@
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
       <c r="J19" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
       <c r="M19" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N19" s="14"/>
       <c r="O19" s="14"/>
       <c r="P19" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
       <c r="S19" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T19" s="14"/>
       <c r="U19" s="14"/>
@@ -1467,10 +1472,10 @@
     <row r="20" ht="45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
@@ -1479,22 +1484,22 @@
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
       <c r="P20" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q20" s="15"/>
       <c r="R20" s="15"/>
       <c r="S20" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T20" s="15"/>
       <c r="U20" s="15"/>
@@ -1506,10 +1511,10 @@
     <row r="21" ht="45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
@@ -1518,22 +1523,22 @@
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
       <c r="J21" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
       <c r="S21" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
@@ -1572,7 +1577,7 @@
     <row r="23" ht="20.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -1601,7 +1606,7 @@
     <row r="24" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -1611,7 +1616,7 @@
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
       <c r="J24" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
@@ -1625,7 +1630,7 @@
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
       <c r="V24" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W24" s="5"/>
       <c r="X24" s="1"/>
@@ -1642,19 +1647,19 @@
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
       <c r="J25" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
       <c r="M25" s="14"/>
       <c r="N25" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O25" s="14"/>
       <c r="P25" s="14"/>
       <c r="Q25" s="14"/>
       <c r="R25" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S25" s="14"/>
       <c r="T25" s="14"/>
@@ -1667,7 +1672,7 @@
     <row r="26" ht="34.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
@@ -1677,19 +1682,19 @@
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
       <c r="J26" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
       <c r="R26" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S26" s="6"/>
       <c r="T26" s="6"/>
@@ -1729,7 +1734,7 @@
     <row r="28" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
@@ -1758,7 +1763,7 @@
     <row r="29" ht="19.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -1768,7 +1773,7 @@
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
       <c r="J29" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" s="14"/>
       <c r="L29" s="14"/>
@@ -1782,7 +1787,7 @@
       <c r="T29" s="14"/>
       <c r="U29" s="14"/>
       <c r="V29" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W29" s="5"/>
       <c r="X29" s="1"/>
@@ -1799,19 +1804,19 @@
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
       <c r="J30" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
       <c r="M30" s="14"/>
       <c r="N30" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O30" s="14"/>
       <c r="P30" s="14"/>
       <c r="Q30" s="14"/>
       <c r="R30" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S30" s="14"/>
       <c r="T30" s="14"/>
@@ -1824,7 +1829,7 @@
     <row r="31" ht="34.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
@@ -1834,19 +1839,19 @@
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
       <c r="J31" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
       <c r="Q31" s="6"/>
       <c r="R31" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S31" s="6"/>
       <c r="T31" s="6"/>
@@ -1886,36 +1891,36 @@
     <row r="33" ht="16.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="19"/>
       <c r="B33" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E33" s="21"/>
       <c r="F33" s="21"/>
       <c r="G33" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H33" s="21"/>
       <c r="I33" s="21"/>
       <c r="J33" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
       <c r="M33" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N33" s="22"/>
       <c r="O33" s="22"/>
       <c r="P33" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q33" s="22"/>
       <c r="R33" s="22"/>
       <c r="S33" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T33" s="23"/>
       <c r="U33" s="23"/>
@@ -1929,27 +1934,27 @@
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
       <c r="G34" s="21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H34" s="21"/>
       <c r="I34" s="21"/>
       <c r="J34" s="22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
       <c r="M34" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N34" s="22"/>
       <c r="O34" s="22"/>
       <c r="P34" s="22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q34" s="22"/>
       <c r="R34" s="22"/>
@@ -1964,7 +1969,7 @@
     <row r="35" ht="16.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -1993,7 +1998,7 @@
     <row r="36" ht="16.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
@@ -2022,12 +2027,12 @@
     <row r="37" ht="16.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
       <c r="E37" s="26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F37" s="26"/>
       <c r="G37" s="26"/>
@@ -2053,12 +2058,12 @@
     <row r="38" ht="16.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
       <c r="E38" s="26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F38" s="26"/>
       <c r="G38" s="26"/>
@@ -2084,12 +2089,12 @@
     <row r="39" ht="16.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
       <c r="E39" s="26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F39" s="26"/>
       <c r="G39" s="26"/>
@@ -2115,12 +2120,12 @@
     <row r="40" ht="16.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C40" s="28"/>
       <c r="D40" s="28"/>
       <c r="E40" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F40" s="26"/>
       <c r="G40" s="26"/>
@@ -2146,12 +2151,12 @@
     <row r="41" ht="16.15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C41" s="28"/>
       <c r="D41" s="28"/>
       <c r="E41" s="26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="26"/>
